--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Midcap Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Midcap Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="257">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Midcap Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -61,15 +61,93 @@
     <t>Listed / Awaiting Listing On Stock Exchanges</t>
   </si>
   <si>
+    <t>BSE Ltd.</t>
+  </si>
+  <si>
+    <t>INE118H01025</t>
+  </si>
+  <si>
+    <t>Capital Markets</t>
+  </si>
+  <si>
     <t>Info Edge (India) Ltd.</t>
   </si>
   <si>
-    <t>INE663F01024</t>
+    <t>INE663F01032</t>
   </si>
   <si>
     <t>Retailing</t>
   </si>
   <si>
+    <t>Jindal Steel &amp; Power Ltd.</t>
+  </si>
+  <si>
+    <t>INE749A01030</t>
+  </si>
+  <si>
+    <t>Ferrous Metals</t>
+  </si>
+  <si>
+    <t>Bharti Hexacom Ltd.</t>
+  </si>
+  <si>
+    <t>INE343G01021</t>
+  </si>
+  <si>
+    <t>Telecom - Services</t>
+  </si>
+  <si>
+    <t>Prestige Estates Projects Ltd.</t>
+  </si>
+  <si>
+    <t>INE811K01011</t>
+  </si>
+  <si>
+    <t>Realty</t>
+  </si>
+  <si>
+    <t>PB Fintech Ltd.</t>
+  </si>
+  <si>
+    <t>INE417T01026</t>
+  </si>
+  <si>
+    <t>Financial Technology (Fintech)</t>
+  </si>
+  <si>
+    <t>APL Apollo Tubes Ltd.</t>
+  </si>
+  <si>
+    <t>INE702C01027</t>
+  </si>
+  <si>
+    <t>Industrial Products</t>
+  </si>
+  <si>
+    <t>Apar Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE372A01015</t>
+  </si>
+  <si>
+    <t>Electrical Equipment</t>
+  </si>
+  <si>
+    <t>Jindal Stainless Ltd.</t>
+  </si>
+  <si>
+    <t>INE220G01021</t>
+  </si>
+  <si>
+    <t>UPL Ltd.</t>
+  </si>
+  <si>
+    <t>INE628A01036</t>
+  </si>
+  <si>
+    <t>Fertilizers &amp; Agrochemicals</t>
+  </si>
+  <si>
     <t>Muthoot Finance Ltd.</t>
   </si>
   <si>
@@ -79,13 +157,118 @@
     <t>Finance</t>
   </si>
   <si>
-    <t>Jindal Stainless Ltd.</t>
-  </si>
-  <si>
-    <t>INE220G01021</t>
-  </si>
-  <si>
-    <t>Ferrous Metals</t>
+    <t>Godrej Properties Ltd.</t>
+  </si>
+  <si>
+    <t>INE484J01027</t>
+  </si>
+  <si>
+    <t>Affle India Ltd.</t>
+  </si>
+  <si>
+    <t>INE00WC01027</t>
+  </si>
+  <si>
+    <t>It - Services</t>
+  </si>
+  <si>
+    <t>KEI Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE878B01027</t>
+  </si>
+  <si>
+    <t>Multi Commodity Exchange Of India Ltd.</t>
+  </si>
+  <si>
+    <t>INE745G01035</t>
+  </si>
+  <si>
+    <t>Bharat Forge Ltd.</t>
+  </si>
+  <si>
+    <t>INE465A01025</t>
+  </si>
+  <si>
+    <t>Auto Components</t>
+  </si>
+  <si>
+    <t>Escorts Kubota Ltd</t>
+  </si>
+  <si>
+    <t>INE042A01014</t>
+  </si>
+  <si>
+    <t>Agricultural, Commercial &amp; Construction Vehicles</t>
+  </si>
+  <si>
+    <t>PI Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE603J01030</t>
+  </si>
+  <si>
+    <t>Nippon Life India Asset Management Ltd</t>
+  </si>
+  <si>
+    <t>INE298J01013</t>
+  </si>
+  <si>
+    <t>SRF Ltd.</t>
+  </si>
+  <si>
+    <t>INE647A01010</t>
+  </si>
+  <si>
+    <t>Chemicals &amp; Petrochemicals</t>
+  </si>
+  <si>
+    <t>Schaeffler India Ltd.</t>
+  </si>
+  <si>
+    <t>INE513A01022</t>
+  </si>
+  <si>
+    <t>Gland Pharma Ltd.</t>
+  </si>
+  <si>
+    <t>INE068V01023</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals &amp; Biotechnology</t>
+  </si>
+  <si>
+    <t>Ambuja Cements Ltd.</t>
+  </si>
+  <si>
+    <t>INE079A01024</t>
+  </si>
+  <si>
+    <t>Cement &amp; Cement Products</t>
+  </si>
+  <si>
+    <t>Hitachi Energy India Ltd.</t>
+  </si>
+  <si>
+    <t>INE07Y701011</t>
+  </si>
+  <si>
+    <t>360 One Wam Ltd.</t>
+  </si>
+  <si>
+    <t>INE466L01038</t>
+  </si>
+  <si>
+    <t>Cummins India Ltd.</t>
+  </si>
+  <si>
+    <t>INE298A01020</t>
+  </si>
+  <si>
+    <t>Supreme Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE195A01028</t>
   </si>
   <si>
     <t>The Phoenix Mills Ltd.</t>
@@ -94,106 +277,211 @@
     <t>INE211B01039</t>
   </si>
   <si>
-    <t>Realty</t>
-  </si>
-  <si>
-    <t>UPL Ltd.</t>
-  </si>
-  <si>
-    <t>INE628A01036</t>
-  </si>
-  <si>
-    <t>Fertilizers &amp; Agrochemicals</t>
-  </si>
-  <si>
-    <t>Jindal Steel &amp; Power Ltd.</t>
-  </si>
-  <si>
-    <t>INE749A01030</t>
-  </si>
-  <si>
-    <t>PB Fintech Ltd.</t>
-  </si>
-  <si>
-    <t>INE417T01026</t>
-  </si>
-  <si>
-    <t>Financial Technology (Fintech)</t>
-  </si>
-  <si>
-    <t>APL Apollo Tubes Ltd.</t>
-  </si>
-  <si>
-    <t>INE702C01027</t>
-  </si>
-  <si>
-    <t>Industrial Products</t>
-  </si>
-  <si>
-    <t>Bharti Hexacom Ltd.</t>
-  </si>
-  <si>
-    <t>INE343G01021</t>
-  </si>
-  <si>
-    <t>Telecom - Services</t>
-  </si>
-  <si>
-    <t>Godrej Properties Ltd.</t>
-  </si>
-  <si>
-    <t>INE484J01027</t>
-  </si>
-  <si>
-    <t>Escorts Kubota Ltd</t>
-  </si>
-  <si>
-    <t>INE042A01014</t>
-  </si>
-  <si>
-    <t>Agricultural, Commercial &amp; Construction Vehicles</t>
-  </si>
-  <si>
-    <t>Prestige Estates Projects Ltd.</t>
-  </si>
-  <si>
-    <t>INE811K01011</t>
-  </si>
-  <si>
-    <t>KEI Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE878B01027</t>
-  </si>
-  <si>
-    <t>Affle India Ltd.</t>
-  </si>
-  <si>
-    <t>INE00WC01027</t>
-  </si>
-  <si>
-    <t>It - Services</t>
-  </si>
-  <si>
-    <t>Bharat Forge Ltd.</t>
-  </si>
-  <si>
-    <t>INE465A01025</t>
-  </si>
-  <si>
-    <t>Auto Components</t>
-  </si>
-  <si>
-    <t>Cummins India Ltd.</t>
-  </si>
-  <si>
-    <t>INE298A01020</t>
-  </si>
-  <si>
-    <t>PI Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE603J01030</t>
+    <t>Navin Fluorine International Ltd.</t>
+  </si>
+  <si>
+    <t>INE048G01026</t>
+  </si>
+  <si>
+    <t>Timken India Ltd.</t>
+  </si>
+  <si>
+    <t>INE325A01013</t>
+  </si>
+  <si>
+    <t>K.P.R. Mill Ltd.</t>
+  </si>
+  <si>
+    <t>INE930H01031</t>
+  </si>
+  <si>
+    <t>Textiles &amp; Apparels</t>
+  </si>
+  <si>
+    <t>Ultratech Cement Ltd.</t>
+  </si>
+  <si>
+    <t>INE481G01011</t>
+  </si>
+  <si>
+    <t>Tata Communications Ltd.</t>
+  </si>
+  <si>
+    <t>INE151A01013</t>
+  </si>
+  <si>
+    <t>Samvardhana Motherson International Ltd.</t>
+  </si>
+  <si>
+    <t>INE775A01035</t>
+  </si>
+  <si>
+    <t>Sundram Fasteners Ltd.</t>
+  </si>
+  <si>
+    <t>INE387A01021</t>
+  </si>
+  <si>
+    <t>Power Finance Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE134E01011</t>
+  </si>
+  <si>
+    <t>BEML Ltd.</t>
+  </si>
+  <si>
+    <t>INE258A01016</t>
+  </si>
+  <si>
+    <t>Vedanta Ltd.</t>
+  </si>
+  <si>
+    <t>INE205A01025</t>
+  </si>
+  <si>
+    <t>Diversified Metals</t>
+  </si>
+  <si>
+    <t>ACC Ltd.</t>
+  </si>
+  <si>
+    <t>INE012A01025</t>
+  </si>
+  <si>
+    <t>Deepak Nitrite Ltd.</t>
+  </si>
+  <si>
+    <t>INE288B01029</t>
+  </si>
+  <si>
+    <t>National Aluminium Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE139A01034</t>
+  </si>
+  <si>
+    <t>Non - Ferrous Metals</t>
+  </si>
+  <si>
+    <t>Grindwell Norton Ltd.</t>
+  </si>
+  <si>
+    <t>INE536A01023</t>
+  </si>
+  <si>
+    <t>Indian Railway Catering and Tourism Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE335Y01020</t>
+  </si>
+  <si>
+    <t>Leisure Services</t>
+  </si>
+  <si>
+    <t>Polycab India Ltd.</t>
+  </si>
+  <si>
+    <t>INE455K01017</t>
+  </si>
+  <si>
+    <t>Crompton Greaves Consumer Electricals Ltd.</t>
+  </si>
+  <si>
+    <t>INE299U01018</t>
+  </si>
+  <si>
+    <t>Consumer Durables</t>
+  </si>
+  <si>
+    <t>JK Cement Ltd.</t>
+  </si>
+  <si>
+    <t>INE823G01014</t>
+  </si>
+  <si>
+    <t>Sona Blw Precision Forgings Ltd.</t>
+  </si>
+  <si>
+    <t>INE073K01018</t>
+  </si>
+  <si>
+    <t>JSW Infrastructure Ltd</t>
+  </si>
+  <si>
+    <t>INE880J01026</t>
+  </si>
+  <si>
+    <t>Transport Infrastructure</t>
+  </si>
+  <si>
+    <t>NMDC Ltd.</t>
+  </si>
+  <si>
+    <t>INE584A01023</t>
+  </si>
+  <si>
+    <t>Minerals &amp; Mining</t>
+  </si>
+  <si>
+    <t>Blue Star Ltd.</t>
+  </si>
+  <si>
+    <t>INE472A01039</t>
+  </si>
+  <si>
+    <t>Kajaria Ceramics Ltd.</t>
+  </si>
+  <si>
+    <t>INE217B01036</t>
+  </si>
+  <si>
+    <t>IRB Infrastructure Developers Ltd.</t>
+  </si>
+  <si>
+    <t>INE821I01022</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>Aarti Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE769A01020</t>
+  </si>
+  <si>
+    <t>IndusInd Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE095A01012</t>
+  </si>
+  <si>
+    <t>Banks</t>
+  </si>
+  <si>
+    <t>Oberoi Realty Ltd.</t>
+  </si>
+  <si>
+    <t>INE093I01010</t>
+  </si>
+  <si>
+    <t>UNO Minda Ltd.</t>
+  </si>
+  <si>
+    <t>INE405E01023</t>
+  </si>
+  <si>
+    <t>Atul Ltd.</t>
+  </si>
+  <si>
+    <t>INE100A01010</t>
+  </si>
+  <si>
+    <t>Hindalco Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE038A01020</t>
   </si>
   <si>
     <t>Dalmia Bharat Ltd.</t>
@@ -202,61 +490,160 @@
     <t>INE00R701025</t>
   </si>
   <si>
-    <t>Cement &amp; Cement Products</t>
-  </si>
-  <si>
-    <t>Interglobe Aviation Ltd.</t>
-  </si>
-  <si>
-    <t>INE646L01027</t>
-  </si>
-  <si>
-    <t>Transport Services</t>
-  </si>
-  <si>
-    <t>SRF Ltd.</t>
-  </si>
-  <si>
-    <t>INE647A01010</t>
-  </si>
-  <si>
-    <t>Chemicals &amp; Petrochemicals</t>
-  </si>
-  <si>
-    <t>Gland Pharma Ltd.</t>
-  </si>
-  <si>
-    <t>INE068V01023</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals &amp; Biotechnology</t>
-  </si>
-  <si>
-    <t>Ambuja Cements Ltd.</t>
-  </si>
-  <si>
-    <t>INE079A01024</t>
-  </si>
-  <si>
-    <t>Multi Commodity Exchange Of India Ltd.</t>
-  </si>
-  <si>
-    <t>INE745G01035</t>
-  </si>
-  <si>
-    <t>Capital Markets</t>
-  </si>
-  <si>
-    <t>Nippon Life India Asset Management Ltd</t>
-  </si>
-  <si>
-    <t>INE298J01013</t>
-  </si>
-  <si>
-    <t>BSE Ltd.</t>
-  </si>
-  <si>
-    <t>INE118H01025</t>
+    <t>Syngene International Ltd.</t>
+  </si>
+  <si>
+    <t>INE398R01022</t>
+  </si>
+  <si>
+    <t>Healthcare Services</t>
+  </si>
+  <si>
+    <t>Piramal Pharma Ltd.</t>
+  </si>
+  <si>
+    <t>INE0DK501011</t>
+  </si>
+  <si>
+    <t>Mphasis Ltd.</t>
+  </si>
+  <si>
+    <t>INE356A01018</t>
+  </si>
+  <si>
+    <t>It - Software</t>
+  </si>
+  <si>
+    <t>Gujarat Fluorochemicals Ltd.</t>
+  </si>
+  <si>
+    <t>INE09N301011</t>
+  </si>
+  <si>
+    <t>Ratnamani Metals &amp; Tubes Ltd.</t>
+  </si>
+  <si>
+    <t>INE703B01027</t>
+  </si>
+  <si>
+    <t>Bandhan Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE545U01014</t>
+  </si>
+  <si>
+    <t>Nuvoco Vistas Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE118D01016</t>
+  </si>
+  <si>
+    <t>Mahindra &amp; Mahindra Ltd.</t>
+  </si>
+  <si>
+    <t>INE101A01026</t>
+  </si>
+  <si>
+    <t>Automobiles</t>
+  </si>
+  <si>
+    <t>UPL Ltd. (Right Share)</t>
+  </si>
+  <si>
+    <t>IN9628A01026</t>
+  </si>
+  <si>
+    <t>Honeywell Automation India Ltd.</t>
+  </si>
+  <si>
+    <t>INE671A01010</t>
+  </si>
+  <si>
+    <t>Industrial Manufacturing</t>
+  </si>
+  <si>
+    <t>Voltas Ltd.</t>
+  </si>
+  <si>
+    <t>INE226A01021</t>
+  </si>
+  <si>
+    <t>SKF India Ltd.</t>
+  </si>
+  <si>
+    <t>INE640A01023</t>
+  </si>
+  <si>
+    <t>Persistent Systems Ltd.</t>
+  </si>
+  <si>
+    <t>INE262H01021</t>
+  </si>
+  <si>
+    <t>HDFC Asset Management Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE127D01025</t>
+  </si>
+  <si>
+    <t>Ge Vernova T&amp;D India Ltd.</t>
+  </si>
+  <si>
+    <t>INE200A01026</t>
+  </si>
+  <si>
+    <t>Jyoti CNC Automation Ltd</t>
+  </si>
+  <si>
+    <t>INE980O01024</t>
+  </si>
+  <si>
+    <t>Astral Ltd.</t>
+  </si>
+  <si>
+    <t>INE006I01046</t>
+  </si>
+  <si>
+    <t>Carborundum Universal Ltd.</t>
+  </si>
+  <si>
+    <t>INE120A01034</t>
+  </si>
+  <si>
+    <t>Chemplast Sanmar Ltd</t>
+  </si>
+  <si>
+    <t>INE488A01050</t>
+  </si>
+  <si>
+    <t>Torrent Power Ltd.</t>
+  </si>
+  <si>
+    <t>INE813H01021</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>Coromandel International Ltd.</t>
+  </si>
+  <si>
+    <t>INE169A01031</t>
+  </si>
+  <si>
+    <t>Hindustan Zinc Ltd.</t>
+  </si>
+  <si>
+    <t>INE267A01025</t>
+  </si>
+  <si>
+    <t>Godrej Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE233A01035</t>
+  </si>
+  <si>
+    <t>Diversified</t>
   </si>
   <si>
     <t>Balkrishna Industries Ltd.</t>
@@ -265,381 +652,12 @@
     <t>INE787D01026</t>
   </si>
   <si>
-    <t>Schaeffler India Ltd.</t>
-  </si>
-  <si>
-    <t>INE513A01022</t>
-  </si>
-  <si>
-    <t>ACC Ltd.</t>
-  </si>
-  <si>
-    <t>INE012A01025</t>
-  </si>
-  <si>
-    <t>Hitachi Energy India Ltd.</t>
-  </si>
-  <si>
-    <t>INE07Y701011</t>
-  </si>
-  <si>
-    <t>Electrical Equipment</t>
-  </si>
-  <si>
-    <t>Navin Fluorine International Ltd.</t>
-  </si>
-  <si>
-    <t>INE048G01026</t>
-  </si>
-  <si>
-    <t>360 One Wam Ltd.</t>
-  </si>
-  <si>
-    <t>INE466L01038</t>
-  </si>
-  <si>
-    <t>Timken India Ltd.</t>
-  </si>
-  <si>
-    <t>INE325A01013</t>
-  </si>
-  <si>
-    <t>Ultratech Cement Ltd.</t>
-  </si>
-  <si>
-    <t>INE481G01011</t>
-  </si>
-  <si>
-    <t>Tata Communications Ltd.</t>
-  </si>
-  <si>
-    <t>INE151A01013</t>
-  </si>
-  <si>
-    <t>Power Finance Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE134E01011</t>
-  </si>
-  <si>
-    <t>Sundram Fasteners Ltd.</t>
-  </si>
-  <si>
-    <t>INE387A01021</t>
-  </si>
-  <si>
-    <t>Grindwell Norton Ltd.</t>
-  </si>
-  <si>
-    <t>INE536A01023</t>
-  </si>
-  <si>
-    <t>K.P.R. Mill Ltd.</t>
-  </si>
-  <si>
-    <t>INE930H01031</t>
-  </si>
-  <si>
-    <t>Textiles &amp; Apparels</t>
-  </si>
-  <si>
-    <t>BEML Ltd.</t>
-  </si>
-  <si>
-    <t>INE258A01016</t>
-  </si>
-  <si>
-    <t>Deepak Nitrite Ltd.</t>
-  </si>
-  <si>
-    <t>INE288B01029</t>
-  </si>
-  <si>
-    <t>SBI Cards &amp; Payment Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE018E01016</t>
-  </si>
-  <si>
-    <t>Coromandel International Ltd.</t>
-  </si>
-  <si>
-    <t>INE169A01031</t>
-  </si>
-  <si>
-    <t>Indus Towers Ltd.</t>
-  </si>
-  <si>
-    <t>INE121J01017</t>
-  </si>
-  <si>
-    <t>Indian Railway Catering and Tourism Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE335Y01020</t>
-  </si>
-  <si>
-    <t>Leisure Services</t>
-  </si>
-  <si>
-    <t>JK Cement Ltd.</t>
-  </si>
-  <si>
-    <t>INE823G01014</t>
-  </si>
-  <si>
-    <t>Crompton Greaves Consumer Electricals Ltd.</t>
-  </si>
-  <si>
-    <t>INE299U01018</t>
-  </si>
-  <si>
-    <t>Consumer Durables</t>
-  </si>
-  <si>
-    <t>JSW Infrastructure Ltd</t>
-  </si>
-  <si>
-    <t>INE880J01026</t>
-  </si>
-  <si>
-    <t>Transport Infrastructure</t>
-  </si>
-  <si>
-    <t>Vedanta Ltd.</t>
-  </si>
-  <si>
-    <t>INE205A01025</t>
-  </si>
-  <si>
-    <t>Diversified Metals</t>
-  </si>
-  <si>
-    <t>National Aluminium Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE139A01034</t>
-  </si>
-  <si>
-    <t>Non - Ferrous Metals</t>
-  </si>
-  <si>
-    <t>Sona Blw Precision Forgings Ltd.</t>
-  </si>
-  <si>
-    <t>INE073K01018</t>
-  </si>
-  <si>
-    <t>IRB Infrastructure Developers Ltd.</t>
-  </si>
-  <si>
-    <t>INE821I01022</t>
-  </si>
-  <si>
-    <t>Construction</t>
-  </si>
-  <si>
-    <t>Polycab India Ltd.</t>
-  </si>
-  <si>
-    <t>INE455K01017</t>
-  </si>
-  <si>
-    <t>NMDC Ltd.</t>
-  </si>
-  <si>
-    <t>INE584A01023</t>
-  </si>
-  <si>
-    <t>Minerals &amp; Mining</t>
-  </si>
-  <si>
-    <t>Kajaria Ceramics Ltd.</t>
-  </si>
-  <si>
-    <t>INE217B01036</t>
-  </si>
-  <si>
-    <t>Apar Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE372A01015</t>
-  </si>
-  <si>
-    <t>3M India Ltd.</t>
-  </si>
-  <si>
-    <t>INE470A01017</t>
-  </si>
-  <si>
-    <t>Diversified</t>
-  </si>
-  <si>
-    <t>Page Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE761H01022</t>
-  </si>
-  <si>
-    <t>Aarti Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE769A01020</t>
-  </si>
-  <si>
-    <t>Samvardhana Motherson International Ltd.</t>
-  </si>
-  <si>
-    <t>INE775A01035</t>
-  </si>
-  <si>
-    <t>Jubilant Foodworks Ltd.</t>
-  </si>
-  <si>
-    <t>INE797F01020</t>
-  </si>
-  <si>
-    <t>Hindalco Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE038A01020</t>
-  </si>
-  <si>
-    <t>Nuvoco Vistas Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE118D01016</t>
-  </si>
-  <si>
-    <t>Atul Ltd.</t>
-  </si>
-  <si>
-    <t>INE100A01010</t>
-  </si>
-  <si>
-    <t>Piramal Pharma Ltd.</t>
-  </si>
-  <si>
-    <t>INE0DK501011</t>
-  </si>
-  <si>
-    <t>Supreme Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE195A01028</t>
-  </si>
-  <si>
-    <t>Mphasis Ltd.</t>
-  </si>
-  <si>
-    <t>INE356A01018</t>
-  </si>
-  <si>
-    <t>It - Software</t>
-  </si>
-  <si>
-    <t>Syngene International Ltd.</t>
-  </si>
-  <si>
-    <t>INE398R01022</t>
-  </si>
-  <si>
-    <t>Healthcare Services</t>
-  </si>
-  <si>
-    <t>Ratnamani Metals &amp; Tubes Ltd.</t>
-  </si>
-  <si>
-    <t>INE703B01027</t>
-  </si>
-  <si>
-    <t>Mahindra &amp; Mahindra Ltd.</t>
-  </si>
-  <si>
-    <t>INE101A01026</t>
-  </si>
-  <si>
-    <t>Automobiles</t>
-  </si>
-  <si>
-    <t>Honeywell Automation India Ltd.</t>
-  </si>
-  <si>
-    <t>INE671A01010</t>
-  </si>
-  <si>
-    <t>Industrial Manufacturing</t>
-  </si>
-  <si>
-    <t>Carborundum Universal Ltd.</t>
-  </si>
-  <si>
-    <t>INE120A01034</t>
-  </si>
-  <si>
-    <t>SKF India Ltd.</t>
-  </si>
-  <si>
-    <t>INE640A01023</t>
-  </si>
-  <si>
-    <t>Go Digit General Insurance Ltd</t>
-  </si>
-  <si>
-    <t>INE03JT01014</t>
-  </si>
-  <si>
-    <t>Insurance</t>
-  </si>
-  <si>
-    <t>Chemplast Sanmar Ltd</t>
-  </si>
-  <si>
-    <t>INE488A01050</t>
-  </si>
-  <si>
-    <t>UPL Ltd. (Right Share)</t>
-  </si>
-  <si>
-    <t>IN9628A01018</t>
-  </si>
-  <si>
-    <t>Torrent Power Ltd.</t>
-  </si>
-  <si>
-    <t>INE813H01021</t>
-  </si>
-  <si>
-    <t>Power</t>
-  </si>
-  <si>
-    <t>Britannia Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE216A01030</t>
-  </si>
-  <si>
-    <t>Food Products</t>
-  </si>
-  <si>
-    <t>Hindustan Zinc Ltd.</t>
-  </si>
-  <si>
-    <t>INE267A01025</t>
-  </si>
-  <si>
     <t>Vardhman Textiles Ltd.</t>
   </si>
   <si>
     <t>INE825A01020</t>
   </si>
   <si>
-    <t>Godrej Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE233A01035</t>
-  </si>
-  <si>
     <t>Gujarat Gas Ltd.</t>
   </si>
   <si>
@@ -655,28 +673,28 @@
     <t>INE669C01036</t>
   </si>
   <si>
+    <t>Hexaware Technologies Ltd.</t>
+  </si>
+  <si>
+    <t>INE093A01041</t>
+  </si>
+  <si>
+    <t>Camlin Fine Sciences Ltd.</t>
+  </si>
+  <si>
+    <t>INE052I01032</t>
+  </si>
+  <si>
     <t>Astec LifeSciences Ltd.</t>
   </si>
   <si>
     <t>INE563J01010</t>
   </si>
   <si>
-    <t>HDFC Asset Management Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE127D01025</t>
-  </si>
-  <si>
-    <t>Grasim Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE047A01021</t>
-  </si>
-  <si>
-    <t>Oberoi Realty Ltd.</t>
-  </si>
-  <si>
-    <t>INE093I01010</t>
+    <t>Endurance Technologies Ltd.</t>
+  </si>
+  <si>
+    <t>INE913H01037</t>
   </si>
   <si>
     <t>CRISIL Ltd.</t>
@@ -685,12 +703,6 @@
     <t>INE007A01025</t>
   </si>
   <si>
-    <t>Endurance Technologies Ltd.</t>
-  </si>
-  <si>
-    <t>INE913H01037</t>
-  </si>
-  <si>
     <t>Unlisted</t>
   </si>
   <si>
@@ -724,6 +736,15 @@
     <t>Treasury Bills</t>
   </si>
   <si>
+    <t>364 Days Treasury Bills</t>
+  </si>
+  <si>
+    <t>IN002024Z198</t>
+  </si>
+  <si>
+    <t>SOV</t>
+  </si>
+  <si>
     <t>Units of Real Estate Investment Trust (REITs)</t>
   </si>
   <si>
@@ -754,7 +775,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -764,9 +785,6 @@
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t>Benchmark name - Nifty Midcap 150 TRI</t>
   </si>
 </sst>
 </file>
@@ -1137,13 +1155,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>141</xdr:row>
+      <xdr:row>145</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>151</xdr:row>
+      <xdr:row>155</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1161,7 +1179,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="27317700"/>
+          <a:off x="666750" y="28079700"/>
           <a:ext cx="3686175" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1176,13 +1194,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>156</xdr:row>
+      <xdr:row>160</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>166</xdr:row>
+      <xdr:row>170</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1200,7 +1218,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="30175200"/>
+          <a:off x="666750" y="30937200"/>
           <a:ext cx="3686175" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1534,7 +1552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J155"/>
+  <dimension ref="B1:J158"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
@@ -1634,10 +1652,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>593352.5799999998</v>
+        <v>635280.5999999999</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9930362636566004</v>
+        <v>0.9894237143496998</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1671,10 +1689,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>593352.5799999998</v>
+        <v>635280.5999999999</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9930362636566004</v>
+        <v>0.9894237143496998</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1697,13 +1715,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>372785</v>
+        <v>997230</v>
       </c>
       <c r="G8" s="15">
-        <v>28792.80</v>
+        <v>26665.93</v>
       </c>
       <c r="H8" s="16">
-        <v>0.0481876973254</v>
+        <v>0.0415311021732</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1726,13 +1744,13 @@
         <v>20</v>
       </c>
       <c r="F9" s="14">
-        <v>948183</v>
+        <v>1863925</v>
       </c>
       <c r="G9" s="15">
-        <v>21417.56</v>
+        <v>26607.53</v>
       </c>
       <c r="H9" s="16">
-        <v>0.0358444784366</v>
+        <v>0.0414401465468</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1755,13 +1773,13 @@
         <v>23</v>
       </c>
       <c r="F10" s="14">
-        <v>3056731</v>
+        <v>2779227</v>
       </c>
       <c r="G10" s="15">
-        <v>19969.62</v>
+        <v>26372.09</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0334212026709</v>
+        <v>0.041073458316</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1784,13 +1802,13 @@
         <v>26</v>
       </c>
       <c r="F11" s="14">
-        <v>1156191</v>
+        <v>1235794</v>
       </c>
       <c r="G11" s="15">
-        <v>18982.34</v>
+        <v>22623.68</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0317688885571</v>
+        <v>0.0352354620902</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1813,13 +1831,13 @@
         <v>29</v>
       </c>
       <c r="F12" s="14">
-        <v>3135084</v>
+        <v>1418018</v>
       </c>
       <c r="G12" s="15">
-        <v>18928.07</v>
+        <v>20796.65</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0316780621584</v>
+        <v>0.0323899371224</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1839,16 +1857,16 @@
         <v>13</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F13" s="14">
-        <v>2279227</v>
+        <v>1158585</v>
       </c>
       <c r="G13" s="15">
-        <v>18041.22</v>
+        <v>20409.63</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0301938279272</v>
+        <v>0.0317871692023</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1859,25 +1877,25 @@
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1">
       <c r="B14" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F14" s="14">
-        <v>983085</v>
+        <v>1117934</v>
       </c>
       <c r="G14" s="15">
-        <v>16975.91</v>
+        <v>20253.61</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0284109226231</v>
+        <v>0.0315441743936</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1888,25 +1906,25 @@
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1">
       <c r="B15" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F15" s="14">
-        <v>1117934</v>
+        <v>247507</v>
       </c>
       <c r="G15" s="15">
-        <v>16875.77</v>
+        <v>20082.72</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0282433280852</v>
+        <v>0.0312780201642</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1917,25 +1935,25 @@
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1">
       <c r="B16" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="F16" s="14">
-        <v>1235794</v>
+        <v>3106731</v>
       </c>
       <c r="G16" s="15">
-        <v>16743.77</v>
+        <v>20030.65</v>
       </c>
       <c r="H16" s="16">
-        <v>0.028022412577</v>
+        <v>0.0311969232555</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1955,16 +1973,16 @@
         <v>13</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="F17" s="14">
-        <v>690323</v>
+        <v>3136084</v>
       </c>
       <c r="G17" s="15">
-        <v>16080.73</v>
+        <v>19691.47</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0269127472844</v>
+        <v>0.030668664191</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1975,25 +1993,25 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
       <c r="B18" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F18" s="14">
-        <v>424690</v>
+        <v>824501</v>
       </c>
       <c r="G18" s="15">
-        <v>15388.43</v>
+        <v>18266</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0257541123876</v>
+        <v>0.0284485526024</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -2004,25 +2022,25 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1">
       <c r="B19" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F19" s="14">
-        <v>1118018</v>
+        <v>740323</v>
       </c>
       <c r="G19" s="15">
-        <v>15199.45</v>
+        <v>16611.37</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0254378350182</v>
+        <v>0.0258715336276</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -2033,25 +2051,25 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1">
       <c r="B20" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="F20" s="14">
-        <v>368592</v>
+        <v>937360</v>
       </c>
       <c r="G20" s="15">
-        <v>14830.67</v>
+        <v>16268.82</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0248206439489</v>
+        <v>0.0253380259251</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -2062,25 +2080,25 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
       <c r="B21" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D21" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="F21" s="14">
-        <v>980740</v>
+        <v>418592</v>
       </c>
       <c r="G21" s="15">
-        <v>14789.07</v>
+        <v>15112.01</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0247510220918</v>
+        <v>0.0235363413671</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -2091,25 +2109,25 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1">
       <c r="B22" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="F22" s="14">
-        <v>1094895</v>
+        <v>224333</v>
       </c>
       <c r="G22" s="15">
-        <v>13402.06</v>
+        <v>14810.46</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0224297189164</v>
+        <v>0.0230666894983</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -2129,16 +2147,16 @@
         <v>13</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="F23" s="14">
-        <v>444068</v>
+        <v>1174895</v>
       </c>
       <c r="G23" s="15">
-        <v>12940.36</v>
+        <v>14579.27</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0216570167181</v>
+        <v>0.0227066204697</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -2149,25 +2167,25 @@
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1">
       <c r="B24" s="12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D24" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="F24" s="14">
-        <v>354480</v>
+        <v>424690</v>
       </c>
       <c r="G24" s="15">
-        <v>12349.20</v>
+        <v>14106.93</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0206676499615</v>
+        <v>0.0219709701173</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -2178,25 +2196,25 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1">
       <c r="B25" s="12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D25" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="F25" s="14">
-        <v>654202</v>
+        <v>354480</v>
       </c>
       <c r="G25" s="15">
-        <v>12209.70</v>
+        <v>13554.25</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0204341824357</v>
+        <v>0.0211101934803</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -2207,25 +2225,25 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
       <c r="B26" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="F26" s="14">
-        <v>280809</v>
+        <v>1644894</v>
       </c>
       <c r="G26" s="15">
-        <v>12143.16</v>
+        <v>12187.84</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0203228209363</v>
+        <v>0.0189820654412</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -2251,10 +2269,10 @@
         <v>417624</v>
       </c>
       <c r="G27" s="15">
-        <v>11734.61</v>
+        <v>11948.22</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0196390707021</v>
+        <v>0.0186088670302</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -2274,16 +2292,16 @@
         <v>13</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="F28" s="14">
-        <v>691034</v>
+        <v>284688</v>
       </c>
       <c r="G28" s="15">
-        <v>10536.54</v>
+        <v>11924.73</v>
       </c>
       <c r="H28" s="16">
-        <v>0.017633977952</v>
+        <v>0.01857228231</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -2294,25 +2312,25 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
       <c r="B29" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="D29" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>62</v>
-      </c>
       <c r="F29" s="14">
-        <v>1960201</v>
+        <v>691034</v>
       </c>
       <c r="G29" s="15">
-        <v>10051.91</v>
+        <v>10977.77</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0168229000521</v>
+        <v>0.0170974305979</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -2335,13 +2353,13 @@
         <v>76</v>
       </c>
       <c r="F30" s="14">
-        <v>174333</v>
+        <v>1960201</v>
       </c>
       <c r="G30" s="15">
-        <v>9994.42</v>
+        <v>10849.71</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0167266846539</v>
+        <v>0.0168979823527</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -2361,16 +2379,16 @@
         <v>13</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="F31" s="14">
-        <v>1579050</v>
+        <v>52215</v>
       </c>
       <c r="G31" s="15">
-        <v>9218.49</v>
+        <v>10076.45</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0154280863937</v>
+        <v>0.0156936613309</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -2390,16 +2408,16 @@
         <v>13</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="F32" s="14">
-        <v>172410</v>
+        <v>984846</v>
       </c>
       <c r="G32" s="15">
-        <v>9147.99</v>
+        <v>9823.35</v>
       </c>
       <c r="H32" s="16">
-        <v>0.015310097429</v>
+        <v>0.0152994683678</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2419,16 +2437,16 @@
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="F33" s="14">
-        <v>327950</v>
+        <v>297397</v>
       </c>
       <c r="G33" s="15">
-        <v>9088.31</v>
+        <v>9719.23</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0152102168417</v>
+        <v>0.0151373056996</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2448,16 +2466,16 @@
         <v>13</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="F34" s="14">
-        <v>265244</v>
+        <v>198401</v>
       </c>
       <c r="G34" s="15">
-        <v>9086.73</v>
+        <v>8226.10</v>
       </c>
       <c r="H34" s="16">
-        <v>0.01520757255</v>
+        <v>0.0128118164109</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2477,16 +2495,16 @@
         <v>13</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="F35" s="14">
-        <v>439840</v>
+        <v>528922</v>
       </c>
       <c r="G35" s="15">
-        <v>8830.45</v>
+        <v>8130.06</v>
       </c>
       <c r="H35" s="16">
-        <v>0.0147786617434</v>
+        <v>0.0126622380143</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2506,16 +2524,16 @@
         <v>13</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="F36" s="14">
-        <v>64215</v>
+        <v>190789</v>
       </c>
       <c r="G36" s="15">
-        <v>8260.33</v>
+        <v>8129.90</v>
       </c>
       <c r="H36" s="16">
-        <v>0.0138245075799</v>
+        <v>0.0126619888208</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2526,25 +2544,25 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
       <c r="B37" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="C37" s="13" t="s">
-        <v>91</v>
-      </c>
       <c r="D37" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="F37" s="14">
-        <v>190789</v>
+        <v>258153</v>
       </c>
       <c r="G37" s="15">
-        <v>7915.26</v>
+        <v>8066.25</v>
       </c>
       <c r="H37" s="16">
-        <v>0.013246997622</v>
+        <v>0.0125628565328</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -2555,25 +2573,25 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
       <c r="B38" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="D38" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="D38" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>76</v>
-      </c>
       <c r="F38" s="14">
-        <v>761689</v>
+        <v>670293</v>
       </c>
       <c r="G38" s="15">
-        <v>7675.92</v>
+        <v>7550.85</v>
       </c>
       <c r="H38" s="16">
-        <v>0.012846437639</v>
+        <v>0.0117601419806</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>13</v>
@@ -2593,16 +2611,16 @@
         <v>13</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="F39" s="14">
-        <v>258153</v>
+        <v>62085</v>
       </c>
       <c r="G39" s="15">
-        <v>7377.50</v>
+        <v>6959.73</v>
       </c>
       <c r="H39" s="16">
-        <v>0.0123470012301</v>
+        <v>0.0108394966059</v>
       </c>
       <c r="I39" s="15" t="s">
         <v>13</v>
@@ -2622,16 +2640,16 @@
         <v>13</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="F40" s="14">
-        <v>62085</v>
+        <v>403597</v>
       </c>
       <c r="G40" s="15">
-        <v>7131.98</v>
+        <v>6765.09</v>
       </c>
       <c r="H40" s="16">
-        <v>0.0119360983847</v>
+        <v>0.0105363527168</v>
       </c>
       <c r="I40" s="15" t="s">
         <v>13</v>
@@ -2651,16 +2669,16 @@
         <v>13</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="F41" s="14">
-        <v>403597</v>
+        <v>4300000</v>
       </c>
       <c r="G41" s="15">
-        <v>6590.74</v>
+        <v>6584.16</v>
       </c>
       <c r="H41" s="16">
-        <v>0.0110302778566</v>
+        <v>0.0102545615954</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>13</v>
@@ -2680,16 +2698,16 @@
         <v>13</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="F42" s="14">
-        <v>1457488</v>
+        <v>586239</v>
       </c>
       <c r="G42" s="15">
-        <v>6157.89</v>
+        <v>6017.74</v>
       </c>
       <c r="H42" s="16">
-        <v>0.0103058590857</v>
+        <v>0.0093723854668</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>13</v>
@@ -2709,16 +2727,16 @@
         <v>13</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F43" s="14">
-        <v>586239</v>
+        <v>1457488</v>
       </c>
       <c r="G43" s="15">
-        <v>6121.51</v>
+        <v>5916.67</v>
       </c>
       <c r="H43" s="16">
-        <v>0.0102449734327</v>
+        <v>0.0092149730497</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>13</v>
@@ -2738,16 +2756,16 @@
         <v>13</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="F44" s="14">
-        <v>301049</v>
+        <v>138229</v>
       </c>
       <c r="G44" s="15">
-        <v>5802.57</v>
+        <v>5847.22</v>
       </c>
       <c r="H44" s="16">
-        <v>0.0097111947038</v>
+        <v>0.0091068074974</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>13</v>
@@ -2770,13 +2788,13 @@
         <v>108</v>
       </c>
       <c r="F45" s="14">
-        <v>608148</v>
+        <v>1278201</v>
       </c>
       <c r="G45" s="15">
-        <v>5667.94</v>
+        <v>5567.20</v>
       </c>
       <c r="H45" s="16">
-        <v>0.0094858776214</v>
+        <v>0.0086706877284</v>
       </c>
       <c r="I45" s="15" t="s">
         <v>13</v>
@@ -2796,16 +2814,16 @@
         <v>13</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="F46" s="14">
-        <v>138229</v>
+        <v>289840</v>
       </c>
       <c r="G46" s="15">
-        <v>5314.49</v>
+        <v>5457.11</v>
       </c>
       <c r="H46" s="16">
-        <v>0.0088943428759</v>
+        <v>0.0084992270279</v>
       </c>
       <c r="I46" s="15" t="s">
         <v>13</v>
@@ -2828,13 +2846,13 @@
         <v>68</v>
       </c>
       <c r="F47" s="14">
-        <v>218880</v>
+        <v>268880</v>
       </c>
       <c r="G47" s="15">
-        <v>5090.27</v>
+        <v>5451</v>
       </c>
       <c r="H47" s="16">
-        <v>0.0085190877603</v>
+        <v>0.0084897109512</v>
       </c>
       <c r="I47" s="15" t="s">
         <v>13</v>
@@ -2854,16 +2872,16 @@
         <v>13</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="F48" s="14">
-        <v>650000</v>
+        <v>3010000</v>
       </c>
       <c r="G48" s="15">
-        <v>5058.30</v>
+        <v>5428.54</v>
       </c>
       <c r="H48" s="16">
-        <v>0.0084655826936</v>
+        <v>0.0084547304141</v>
       </c>
       <c r="I48" s="15" t="s">
         <v>13</v>
@@ -2874,25 +2892,25 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
       <c r="B49" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D49" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F49" s="14">
-        <v>265446</v>
+        <v>301049</v>
       </c>
       <c r="G49" s="15">
-        <v>4803.38</v>
+        <v>5408.65</v>
       </c>
       <c r="H49" s="16">
-        <v>0.0080389479862</v>
+        <v>0.0084237525475</v>
       </c>
       <c r="I49" s="15" t="s">
         <v>13</v>
@@ -2903,25 +2921,25 @@
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
       <c r="B50" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D50" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="F50" s="14">
-        <v>1371668</v>
+        <v>676816</v>
       </c>
       <c r="G50" s="15">
-        <v>4762.43</v>
+        <v>5116.73</v>
       </c>
       <c r="H50" s="16">
-        <v>0.0079704139706</v>
+        <v>0.0079690990122</v>
       </c>
       <c r="I50" s="15" t="s">
         <v>13</v>
@@ -2932,25 +2950,25 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1">
       <c r="B51" s="12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D51" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>121</v>
+        <v>35</v>
       </c>
       <c r="F51" s="14">
-        <v>576816</v>
+        <v>81210</v>
       </c>
       <c r="G51" s="15">
-        <v>4743.16</v>
+        <v>4865.29</v>
       </c>
       <c r="H51" s="16">
-        <v>0.0079381636536</v>
+        <v>0.0075774914316</v>
       </c>
       <c r="I51" s="15" t="s">
         <v>13</v>
@@ -2961,25 +2979,25 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
       <c r="B52" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D52" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="F52" s="14">
-        <v>98042</v>
+        <v>1347367</v>
       </c>
       <c r="G52" s="15">
-        <v>4740.18</v>
+        <v>4754.86</v>
       </c>
       <c r="H52" s="16">
-        <v>0.0079331763186</v>
+        <v>0.0074055011949</v>
       </c>
       <c r="I52" s="15" t="s">
         <v>13</v>
@@ -2990,25 +3008,25 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1">
       <c r="B53" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D53" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="F53" s="14">
-        <v>1347367</v>
+        <v>83610</v>
       </c>
       <c r="G53" s="15">
-        <v>4626.86</v>
+        <v>4596.46</v>
       </c>
       <c r="H53" s="16">
-        <v>0.007743523702</v>
+        <v>0.0071587996329</v>
       </c>
       <c r="I53" s="15" t="s">
         <v>13</v>
@@ -3019,25 +3037,25 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1">
       <c r="B54" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D54" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>129</v>
+        <v>58</v>
       </c>
       <c r="F54" s="14">
-        <v>1634371</v>
+        <v>795652</v>
       </c>
       <c r="G54" s="15">
-        <v>4494.52</v>
+        <v>4327.95</v>
       </c>
       <c r="H54" s="16">
-        <v>0.0075220391689</v>
+        <v>0.0067406062211</v>
       </c>
       <c r="I54" s="15" t="s">
         <v>13</v>
@@ -3060,13 +3078,13 @@
         <v>132</v>
       </c>
       <c r="F55" s="14">
-        <v>1008201</v>
+        <v>1371879</v>
       </c>
       <c r="G55" s="15">
-        <v>4450.20</v>
+        <v>3990.11</v>
       </c>
       <c r="H55" s="16">
-        <v>0.0074478651134</v>
+        <v>0.0062144341522</v>
       </c>
       <c r="I55" s="15" t="s">
         <v>13</v>
@@ -3089,13 +3107,13 @@
         <v>135</v>
       </c>
       <c r="F56" s="14">
-        <v>2200000</v>
+        <v>5400000</v>
       </c>
       <c r="G56" s="15">
-        <v>4449.28</v>
+        <v>3843.18</v>
       </c>
       <c r="H56" s="16">
-        <v>0.0074463253992</v>
+        <v>0.0059855966489</v>
       </c>
       <c r="I56" s="15" t="s">
         <v>13</v>
@@ -3115,16 +3133,16 @@
         <v>13</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>55</v>
+        <v>125</v>
       </c>
       <c r="F57" s="14">
-        <v>795652</v>
+        <v>246883</v>
       </c>
       <c r="G57" s="15">
-        <v>4012.47</v>
+        <v>3782.99</v>
       </c>
       <c r="H57" s="16">
-        <v>0.0067152791631</v>
+        <v>0.0058918531703</v>
       </c>
       <c r="I57" s="15" t="s">
         <v>13</v>
@@ -3144,16 +3162,16 @@
         <v>13</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="F58" s="14">
-        <v>6977439</v>
+        <v>359400</v>
       </c>
       <c r="G58" s="15">
-        <v>3999.47</v>
+        <v>3736.86</v>
       </c>
       <c r="H58" s="16">
-        <v>0.0066935223327</v>
+        <v>0.0058200075702</v>
       </c>
       <c r="I58" s="15" t="s">
         <v>13</v>
@@ -3164,25 +3182,25 @@
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1">
       <c r="B59" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="C59" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="C59" s="13" t="s">
+      <c r="D59" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="D59" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E59" s="13" t="s">
-        <v>37</v>
-      </c>
       <c r="F59" s="14">
-        <v>62742</v>
+        <v>6977439</v>
       </c>
       <c r="G59" s="15">
-        <v>3788.33</v>
+        <v>3577.33</v>
       </c>
       <c r="H59" s="16">
-        <v>0.0063401579356</v>
+        <v>0.0055715460791</v>
       </c>
       <c r="I59" s="15" t="s">
         <v>13</v>
@@ -3202,16 +3220,16 @@
         <v>13</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>145</v>
+        <v>68</v>
       </c>
       <c r="F60" s="14">
-        <v>5400000</v>
+        <v>700000</v>
       </c>
       <c r="G60" s="15">
-        <v>3569.40</v>
+        <v>3284.75</v>
       </c>
       <c r="H60" s="16">
-        <v>0.0059737561763</v>
+        <v>0.0051158646206</v>
       </c>
       <c r="I60" s="15" t="s">
         <v>13</v>
@@ -3222,25 +3240,25 @@
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1">
       <c r="B61" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="C61" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="C61" s="13" t="s">
+      <c r="D61" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="D61" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E61" s="13" t="s">
-        <v>126</v>
-      </c>
       <c r="F61" s="14">
-        <v>359400</v>
+        <v>400000</v>
       </c>
       <c r="G61" s="15">
-        <v>3563.09</v>
+        <v>3267.80</v>
       </c>
       <c r="H61" s="16">
-        <v>0.0059631957455</v>
+        <v>0.0050894656845</v>
       </c>
       <c r="I61" s="15" t="s">
         <v>13</v>
@@ -3260,16 +3278,16 @@
         <v>13</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="F62" s="14">
-        <v>46524</v>
+        <v>181349</v>
       </c>
       <c r="G62" s="15">
-        <v>3485.55</v>
+        <v>3166.90</v>
       </c>
       <c r="H62" s="16">
-        <v>0.0058334246204</v>
+        <v>0.0049323180355</v>
       </c>
       <c r="I62" s="15" t="s">
         <v>13</v>
@@ -3289,16 +3307,16 @@
         <v>13</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>152</v>
+        <v>58</v>
       </c>
       <c r="F63" s="14">
-        <v>11434</v>
+        <v>311633</v>
       </c>
       <c r="G63" s="15">
-        <v>3417.88</v>
+        <v>3137.05</v>
       </c>
       <c r="H63" s="16">
-        <v>0.0057201719504</v>
+        <v>0.0048858278737</v>
       </c>
       <c r="I63" s="15" t="s">
         <v>13</v>
@@ -3309,25 +3327,25 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1">
       <c r="B64" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="C64" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="C64" s="13" t="s">
-        <v>154</v>
-      </c>
       <c r="D64" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="F64" s="14">
-        <v>7344</v>
+        <v>41068</v>
       </c>
       <c r="G64" s="15">
-        <v>3284.50</v>
+        <v>2930.82</v>
       </c>
       <c r="H64" s="16">
-        <v>0.0054969468709</v>
+        <v>0.0045646330306</v>
       </c>
       <c r="I64" s="15" t="s">
         <v>13</v>
@@ -3338,25 +3356,25 @@
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1">
       <c r="B65" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="C65" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="C65" s="13" t="s">
-        <v>156</v>
-      </c>
       <c r="D65" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>68</v>
+        <v>115</v>
       </c>
       <c r="F65" s="14">
-        <v>700000</v>
+        <v>450000</v>
       </c>
       <c r="G65" s="15">
-        <v>3112.90</v>
+        <v>2850.75</v>
       </c>
       <c r="H65" s="16">
-        <v>0.0052097567101</v>
+        <v>0.00443992726</v>
       </c>
       <c r="I65" s="15" t="s">
         <v>13</v>
@@ -3367,25 +3385,25 @@
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1">
       <c r="B66" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C66" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="C66" s="13" t="s">
-        <v>158</v>
-      </c>
       <c r="D66" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="F66" s="14">
-        <v>2200000</v>
+        <v>137180</v>
       </c>
       <c r="G66" s="15">
-        <v>3107.72</v>
+        <v>2766.10</v>
       </c>
       <c r="H66" s="16">
-        <v>0.00520108745</v>
+        <v>0.0043080883254</v>
       </c>
       <c r="I66" s="15" t="s">
         <v>13</v>
@@ -3396,25 +3414,25 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1">
       <c r="B67" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="C67" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="C67" s="13" t="s">
+      <c r="D67" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="D67" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E67" s="13" t="s">
-        <v>121</v>
-      </c>
       <c r="F67" s="14">
-        <v>401800</v>
+        <v>413238</v>
       </c>
       <c r="G67" s="15">
-        <v>2828.27</v>
+        <v>2671.79</v>
       </c>
       <c r="H67" s="16">
-        <v>0.0047333992774</v>
+        <v>0.0041612043336</v>
       </c>
       <c r="I67" s="15" t="s">
         <v>13</v>
@@ -3434,16 +3452,16 @@
         <v>13</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>135</v>
+        <v>73</v>
       </c>
       <c r="F68" s="14">
-        <v>450000</v>
+        <v>1091460</v>
       </c>
       <c r="G68" s="15">
-        <v>2674.35</v>
+        <v>2251.68</v>
       </c>
       <c r="H68" s="16">
-        <v>0.0044757984059</v>
+        <v>0.0035069000834</v>
       </c>
       <c r="I68" s="15" t="s">
         <v>13</v>
@@ -3463,16 +3481,16 @@
         <v>13</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>62</v>
+        <v>165</v>
       </c>
       <c r="F69" s="14">
-        <v>740781</v>
+        <v>76085</v>
       </c>
       <c r="G69" s="15">
-        <v>2596.44</v>
+        <v>1946.86</v>
       </c>
       <c r="H69" s="16">
-        <v>0.0043454080479</v>
+        <v>0.0030321553224</v>
       </c>
       <c r="I69" s="15" t="s">
         <v>13</v>
@@ -3483,10 +3501,10 @@
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1">
       <c r="B70" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D70" s="13" t="s">
         <v>13</v>
@@ -3495,13 +3513,13 @@
         <v>68</v>
       </c>
       <c r="F70" s="14">
-        <v>41068</v>
+        <v>50215</v>
       </c>
       <c r="G70" s="15">
-        <v>2581.41</v>
+        <v>1784.29</v>
       </c>
       <c r="H70" s="16">
-        <v>0.0043202538048</v>
+        <v>0.0027789591548</v>
       </c>
       <c r="I70" s="15" t="s">
         <v>13</v>
@@ -3512,25 +3530,25 @@
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1">
       <c r="B71" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D71" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="F71" s="14">
-        <v>1091460</v>
+        <v>61301</v>
       </c>
       <c r="G71" s="15">
-        <v>2542.01</v>
+        <v>1740.34</v>
       </c>
       <c r="H71" s="16">
-        <v>0.0042543138728</v>
+        <v>0.0027105088161</v>
       </c>
       <c r="I71" s="15" t="s">
         <v>13</v>
@@ -3541,25 +3559,25 @@
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1">
       <c r="B72" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D72" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>37</v>
+        <v>147</v>
       </c>
       <c r="F72" s="14">
-        <v>63444</v>
+        <v>1000000</v>
       </c>
       <c r="G72" s="15">
-        <v>2517.97</v>
+        <v>1701.90</v>
       </c>
       <c r="H72" s="16">
-        <v>0.0042140804727</v>
+        <v>0.0026506400785</v>
       </c>
       <c r="I72" s="15" t="s">
         <v>13</v>
@@ -3570,25 +3588,25 @@
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1">
       <c r="B73" s="12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D73" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>173</v>
+        <v>76</v>
       </c>
       <c r="F73" s="14">
-        <v>76085</v>
+        <v>456635</v>
       </c>
       <c r="G73" s="15">
-        <v>2182.08</v>
+        <v>1634.07</v>
       </c>
       <c r="H73" s="16">
-        <v>0.0036519341842</v>
+        <v>0.0025449976103</v>
       </c>
       <c r="I73" s="15" t="s">
         <v>13</v>
@@ -3611,13 +3629,13 @@
         <v>176</v>
       </c>
       <c r="F74" s="14">
-        <v>254903</v>
+        <v>52857</v>
       </c>
       <c r="G74" s="15">
-        <v>1903.23</v>
+        <v>1573.45</v>
       </c>
       <c r="H74" s="16">
-        <v>0.0031852501729</v>
+        <v>0.0024505844241</v>
       </c>
       <c r="I74" s="15" t="s">
         <v>13</v>
@@ -3637,16 +3655,16 @@
         <v>13</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F75" s="14">
-        <v>61301</v>
+        <v>329385</v>
       </c>
       <c r="G75" s="15">
-        <v>1752.35</v>
+        <v>1349.98</v>
       </c>
       <c r="H75" s="16">
-        <v>0.0029327370526</v>
+        <v>0.0021025389818</v>
       </c>
       <c r="I75" s="15" t="s">
         <v>13</v>
@@ -3669,13 +3687,13 @@
         <v>181</v>
       </c>
       <c r="F76" s="14">
-        <v>52857</v>
+        <v>3370</v>
       </c>
       <c r="G76" s="15">
-        <v>1580.35</v>
+        <v>1298.46</v>
       </c>
       <c r="H76" s="16">
-        <v>0.0026448774509</v>
+        <v>0.0020222986757</v>
       </c>
       <c r="I76" s="15" t="s">
         <v>13</v>
@@ -3695,16 +3713,16 @@
         <v>13</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>184</v>
+        <v>125</v>
       </c>
       <c r="F77" s="14">
-        <v>3370</v>
+        <v>100000</v>
       </c>
       <c r="G77" s="15">
-        <v>1363.91</v>
+        <v>1262.80</v>
       </c>
       <c r="H77" s="16">
-        <v>0.0022826429614</v>
+        <v>0.0019667596751</v>
       </c>
       <c r="I77" s="15" t="s">
         <v>13</v>
@@ -3715,25 +3733,25 @@
     </row>
     <row r="78" spans="2:10" ht="15" customHeight="1">
       <c r="B78" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="C78" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="C78" s="13" t="s">
-        <v>186</v>
-      </c>
       <c r="D78" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F78" s="14">
-        <v>91207</v>
+        <v>24998</v>
       </c>
       <c r="G78" s="15">
-        <v>1082.35</v>
+        <v>1173.91</v>
       </c>
       <c r="H78" s="16">
-        <v>0.0018114234878</v>
+        <v>0.0018283171129</v>
       </c>
       <c r="I78" s="15" t="s">
         <v>13</v>
@@ -3744,25 +3762,25 @@
     </row>
     <row r="79" spans="2:10" ht="15" customHeight="1">
       <c r="B79" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C79" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="C79" s="13" t="s">
-        <v>188</v>
-      </c>
       <c r="D79" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>37</v>
+        <v>165</v>
       </c>
       <c r="F79" s="14">
-        <v>24998</v>
+        <v>20000</v>
       </c>
       <c r="G79" s="15">
-        <v>1010.88</v>
+        <v>1127.6</v>
       </c>
       <c r="H79" s="16">
-        <v>0.0016918111289</v>
+        <v>0.0017561911701</v>
       </c>
       <c r="I79" s="15" t="s">
         <v>13</v>
@@ -3773,25 +3791,25 @@
     </row>
     <row r="80" spans="2:10" ht="15" customHeight="1">
       <c r="B80" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="C80" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="C80" s="13" t="s">
-        <v>190</v>
-      </c>
       <c r="D80" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>191</v>
+        <v>17</v>
       </c>
       <c r="F80" s="14">
-        <v>335893</v>
+        <v>22579</v>
       </c>
       <c r="G80" s="15">
-        <v>999.95</v>
+        <v>1079.95</v>
       </c>
       <c r="H80" s="16">
-        <v>0.0016735186553</v>
+        <v>0.0016819782318</v>
       </c>
       <c r="I80" s="15" t="s">
         <v>13</v>
@@ -3802,25 +3820,25 @@
     </row>
     <row r="81" spans="2:10" ht="15" customHeight="1">
       <c r="B81" s="12" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D81" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F81" s="14">
-        <v>187205</v>
+        <v>47319</v>
       </c>
       <c r="G81" s="15">
-        <v>888.47</v>
+        <v>1060.61</v>
       </c>
       <c r="H81" s="16">
-        <v>0.001486945467</v>
+        <v>0.0016518569678</v>
       </c>
       <c r="I81" s="15" t="s">
         <v>13</v>
@@ -3831,25 +3849,25 @@
     </row>
     <row r="82" spans="2:10" ht="15" customHeight="1">
       <c r="B82" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D82" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>29</v>
+        <v>181</v>
       </c>
       <c r="F82" s="14">
-        <v>329385</v>
+        <v>79197</v>
       </c>
       <c r="G82" s="15">
-        <v>866.94</v>
+        <v>1026.08</v>
       </c>
       <c r="H82" s="16">
-        <v>0.0014509128087</v>
+        <v>0.0015980778963</v>
       </c>
       <c r="I82" s="15" t="s">
         <v>13</v>
@@ -3860,25 +3878,25 @@
     </row>
     <row r="83" spans="2:10" ht="15" customHeight="1">
       <c r="B83" s="12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D83" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>198</v>
+        <v>35</v>
       </c>
       <c r="F83" s="14">
-        <v>50000</v>
+        <v>61509</v>
       </c>
       <c r="G83" s="15">
-        <v>731.73</v>
+        <v>921.47</v>
       </c>
       <c r="H83" s="16">
-        <v>0.0012246250369</v>
+        <v>0.001435152073</v>
       </c>
       <c r="I83" s="15" t="s">
         <v>13</v>
@@ -3889,25 +3907,25 @@
     </row>
     <row r="84" spans="2:10" ht="15" customHeight="1">
       <c r="B84" s="12" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D84" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>201</v>
+        <v>35</v>
       </c>
       <c r="F84" s="14">
-        <v>13769</v>
+        <v>91207</v>
       </c>
       <c r="G84" s="15">
-        <v>706.30</v>
+        <v>904.59</v>
       </c>
       <c r="H84" s="16">
-        <v>0.0011820653295</v>
+        <v>0.0014088621591</v>
       </c>
       <c r="I84" s="15" t="s">
         <v>13</v>
@@ -3918,25 +3936,25 @@
     </row>
     <row r="85" spans="2:10" ht="15" customHeight="1">
       <c r="B85" s="12" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D85" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>135</v>
+        <v>68</v>
       </c>
       <c r="F85" s="14">
-        <v>128384</v>
+        <v>187205</v>
       </c>
       <c r="G85" s="15">
-        <v>577.92</v>
+        <v>794.59</v>
       </c>
       <c r="H85" s="16">
-        <v>0.0009672082617</v>
+        <v>0.0012375416299</v>
       </c>
       <c r="I85" s="15" t="s">
         <v>13</v>
@@ -3947,25 +3965,25 @@
     </row>
     <row r="86" spans="2:10" ht="15" customHeight="1">
       <c r="B86" s="12" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D86" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>108</v>
+        <v>202</v>
       </c>
       <c r="F86" s="14">
-        <v>67032</v>
+        <v>50000</v>
       </c>
       <c r="G86" s="15">
-        <v>306.17</v>
+        <v>687</v>
       </c>
       <c r="H86" s="16">
-        <v>0.000512406827</v>
+        <v>0.0010699745777</v>
       </c>
       <c r="I86" s="15" t="s">
         <v>13</v>
@@ -3976,25 +3994,25 @@
     </row>
     <row r="87" spans="2:10" ht="15" customHeight="1">
       <c r="B87" s="12" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D87" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>152</v>
+        <v>43</v>
       </c>
       <c r="F87" s="14">
-        <v>33260</v>
+        <v>29996</v>
       </c>
       <c r="G87" s="15">
-        <v>296.20</v>
+        <v>686.73</v>
       </c>
       <c r="H87" s="16">
-        <v>0.0004957210117</v>
+        <v>0.0010695540637</v>
       </c>
       <c r="I87" s="15" t="s">
         <v>13</v>
@@ -4005,25 +4023,25 @@
     </row>
     <row r="88" spans="2:10" ht="15" customHeight="1">
       <c r="B88" s="12" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D88" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>210</v>
+        <v>115</v>
       </c>
       <c r="F88" s="14">
-        <v>54650</v>
+        <v>128384</v>
       </c>
       <c r="G88" s="15">
-        <v>265.6</v>
+        <v>588.26</v>
       </c>
       <c r="H88" s="16">
-        <v>0.0004445087803</v>
+        <v>0.0009161910409</v>
       </c>
       <c r="I88" s="15" t="s">
         <v>13</v>
@@ -4034,25 +4052,25 @@
     </row>
     <row r="89" spans="2:10" ht="15" customHeight="1">
       <c r="B89" s="12" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D89" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>173</v>
+        <v>209</v>
       </c>
       <c r="F89" s="14">
-        <v>15372</v>
+        <v>33260</v>
       </c>
       <c r="G89" s="15">
-        <v>257.4</v>
+        <v>394.03</v>
       </c>
       <c r="H89" s="16">
-        <v>0.0004307852411</v>
+        <v>0.0006136857101</v>
       </c>
       <c r="I89" s="15" t="s">
         <v>13</v>
@@ -4063,25 +4081,25 @@
     </row>
     <row r="90" spans="2:10" ht="15" customHeight="1">
       <c r="B90" s="12" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D90" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="F90" s="14">
-        <v>15844</v>
+        <v>13827</v>
       </c>
       <c r="G90" s="15">
-        <v>155.44</v>
+        <v>341.83</v>
       </c>
       <c r="H90" s="16">
-        <v>0.000260144747</v>
+        <v>0.0005323863317</v>
       </c>
       <c r="I90" s="15" t="s">
         <v>13</v>
@@ -4092,25 +4110,25 @@
     </row>
     <row r="91" spans="2:10" ht="15" customHeight="1">
       <c r="B91" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D91" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F91" s="14">
-        <v>2579</v>
+        <v>67032</v>
       </c>
       <c r="G91" s="15">
-        <v>99.80</v>
+        <v>329.63</v>
       </c>
       <c r="H91" s="16">
-        <v>0.000167025513</v>
+        <v>0.0005133853276</v>
       </c>
       <c r="I91" s="15" t="s">
         <v>13</v>
@@ -4121,25 +4139,25 @@
     </row>
     <row r="92" spans="2:10" ht="15" customHeight="1">
       <c r="B92" s="12" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C92" s="13" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D92" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>62</v>
+        <v>216</v>
       </c>
       <c r="F92" s="14">
-        <v>3975</v>
+        <v>54650</v>
       </c>
       <c r="G92" s="15">
-        <v>99.73</v>
+        <v>251.42</v>
       </c>
       <c r="H92" s="16">
-        <v>0.0001669083609</v>
+        <v>0.0003915764313</v>
       </c>
       <c r="I92" s="15" t="s">
         <v>13</v>
@@ -4150,25 +4168,25 @@
     </row>
     <row r="93" spans="2:10" ht="15" customHeight="1">
       <c r="B93" s="12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C93" s="13" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D93" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>26</v>
+        <v>165</v>
       </c>
       <c r="F93" s="14">
-        <v>4169</v>
+        <v>15372</v>
       </c>
       <c r="G93" s="15">
-        <v>75.57</v>
+        <v>241.94</v>
       </c>
       <c r="H93" s="16">
-        <v>0.0001264741284</v>
+        <v>0.0003768117166</v>
       </c>
       <c r="I93" s="15" t="s">
         <v>13</v>
@@ -4179,25 +4197,25 @@
     </row>
     <row r="94" spans="2:10" ht="15" customHeight="1">
       <c r="B94" s="12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C94" s="13" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D94" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>20</v>
+        <v>165</v>
       </c>
       <c r="F94" s="14">
-        <v>865</v>
+        <v>24881</v>
       </c>
       <c r="G94" s="15">
-        <v>47</v>
+        <v>213.35</v>
       </c>
       <c r="H94" s="16">
-        <v>0.0000786593097</v>
+        <v>0.0003322839536</v>
       </c>
       <c r="I94" s="15" t="s">
         <v>13</v>
@@ -4208,25 +4226,25 @@
     </row>
     <row r="95" spans="2:10" ht="15" customHeight="1">
       <c r="B95" s="12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D95" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E95" s="13" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="F95" s="14">
-        <v>1880</v>
+        <v>82527</v>
       </c>
       <c r="G95" s="15">
-        <v>37.40</v>
+        <v>191.79</v>
       </c>
       <c r="H95" s="16">
-        <v>0.0000625927273</v>
+        <v>0.0002987051299</v>
       </c>
       <c r="I95" s="15" t="s">
         <v>13</v>
@@ -4237,6 +4255,27 @@
     </row>
     <row r="96" spans="2:10" ht="15" customHeight="1">
       <c r="B96" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="C96" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="D96" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E96" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F96" s="14">
+        <v>15844</v>
+      </c>
+      <c r="G96" s="15">
+        <v>106.50</v>
+      </c>
+      <c r="H96" s="16">
+        <v>0.0001658694214</v>
+      </c>
+      <c r="I96" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J96" s="11" t="s">
@@ -4244,28 +4283,28 @@
       </c>
     </row>
     <row r="97" spans="2:10" ht="15" customHeight="1">
-      <c r="B97" s="7" t="s">
+      <c r="B97" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="C97" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D97" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E97" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F97" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G97" s="9" t="s">
+      <c r="C97" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="H97" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="I97" s="9" t="s">
+      <c r="D97" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E97" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F97" s="14">
+        <v>1880</v>
+      </c>
+      <c r="G97" s="15">
+        <v>45.72</v>
+      </c>
+      <c r="H97" s="16">
+        <v>0.0000712070417</v>
+      </c>
+      <c r="I97" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J97" s="11" t="s">
@@ -4274,6 +4313,27 @@
     </row>
     <row r="98" spans="2:10" ht="15" customHeight="1">
       <c r="B98" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C98" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="D98" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E98" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="F98" s="14">
+        <v>865</v>
+      </c>
+      <c r="G98" s="15">
+        <v>45.41</v>
+      </c>
+      <c r="H98" s="16">
+        <v>0.0000707242293</v>
+      </c>
+      <c r="I98" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J98" s="11" t="s">
@@ -4281,28 +4341,7 @@
       </c>
     </row>
     <row r="99" spans="2:10" ht="15" customHeight="1">
-      <c r="B99" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="C99" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D99" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E99" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F99" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G99" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="I99" s="9" t="s">
+      <c r="B99" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J99" s="11" t="s">
@@ -4310,7 +4349,28 @@
       </c>
     </row>
     <row r="100" spans="2:10" ht="15" customHeight="1">
-      <c r="B100" s="12" t="s">
+      <c r="B100" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F100" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G100" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="H100" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="I100" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J100" s="11" t="s">
@@ -4318,73 +4378,73 @@
       </c>
     </row>
     <row r="101" spans="2:10" ht="15" customHeight="1">
-      <c r="B101" s="7" t="s">
+      <c r="B101" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J101" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="102" spans="2:10" ht="15" customHeight="1">
+      <c r="B102" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D102" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E102" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F102" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G102" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="H102" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="I102" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J102" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="103" spans="2:10" ht="15" customHeight="1">
+      <c r="B103" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J103" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="104" spans="2:10" ht="15" customHeight="1">
+      <c r="B104" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C101" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D101" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E101" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F101" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G101" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="I101" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J101" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="102" spans="2:10" ht="15" customHeight="1">
-      <c r="B102" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J102" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="103" spans="2:10" ht="15" customHeight="1">
-      <c r="B103" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="C103" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D103" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E103" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F103" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G103" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="I103" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J103" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="104" spans="2:10" ht="15" customHeight="1">
-      <c r="B104" s="12" t="s">
+      <c r="C104" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D104" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E104" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F104" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G104" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="H104" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="I104" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J104" s="11" t="s">
@@ -4392,28 +4452,7 @@
       </c>
     </row>
     <row r="105" spans="2:10" ht="15" customHeight="1">
-      <c r="B105" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="C105" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D105" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E105" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F105" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G105" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="I105" s="9" t="s">
+      <c r="B105" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J105" s="11" t="s">
@@ -4421,7 +4460,28 @@
       </c>
     </row>
     <row r="106" spans="2:10" ht="15" customHeight="1">
-      <c r="B106" s="12" t="s">
+      <c r="B106" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D106" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E106" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F106" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G106" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="H106" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="I106" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J106" s="11" t="s">
@@ -4429,36 +4489,36 @@
       </c>
     </row>
     <row r="107" spans="2:10" ht="15" customHeight="1">
-      <c r="B107" s="7" t="s">
+      <c r="B107" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J107" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="108" spans="2:10" ht="15" customHeight="1">
+      <c r="B108" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="C108" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E108" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F108" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G108" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="C107" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D107" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E107" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F107" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G107" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="I107" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J107" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="108" spans="2:10" ht="15" customHeight="1">
-      <c r="B108" s="12" t="s">
+      <c r="H108" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="I108" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J108" s="11" t="s">
@@ -4466,28 +4526,7 @@
       </c>
     </row>
     <row r="109" spans="2:10" ht="15" customHeight="1">
-      <c r="B109" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="C109" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D109" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E109" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F109" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G109" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="I109" s="9" t="s">
+      <c r="B109" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J109" s="11" t="s">
@@ -4495,7 +4534,28 @@
       </c>
     </row>
     <row r="110" spans="2:10" ht="15" customHeight="1">
-      <c r="B110" s="12" t="s">
+      <c r="B110" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D110" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E110" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F110" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G110" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="H110" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="I110" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J110" s="11" t="s">
@@ -4503,28 +4563,7 @@
       </c>
     </row>
     <row r="111" spans="2:10" ht="15" customHeight="1">
-      <c r="B111" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="C111" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D111" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E111" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F111" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G111" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="H111" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="I111" s="9" t="s">
+      <c r="B111" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J111" s="11" t="s">
@@ -4532,7 +4571,28 @@
       </c>
     </row>
     <row r="112" spans="2:10" ht="15" customHeight="1">
-      <c r="B112" s="12" t="s">
+      <c r="B112" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D112" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E112" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F112" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G112" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="H112" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="I112" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J112" s="11" t="s">
@@ -4540,28 +4600,7 @@
       </c>
     </row>
     <row r="113" spans="2:10" ht="15" customHeight="1">
-      <c r="B113" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="C113" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D113" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E113" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F113" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G113" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="H113" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="I113" s="9" t="s">
+      <c r="B113" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J113" s="11" t="s">
@@ -4569,7 +4608,28 @@
       </c>
     </row>
     <row r="114" spans="2:10" ht="15" customHeight="1">
-      <c r="B114" s="12" t="s">
+      <c r="B114" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="C114" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D114" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E114" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F114" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G114" s="9">
+        <v>494.90</v>
+      </c>
+      <c r="H114" s="10">
+        <v>0.0007707866354</v>
+      </c>
+      <c r="I114" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J114" s="11" t="s">
@@ -4577,28 +4637,7 @@
       </c>
     </row>
     <row r="115" spans="2:10" ht="15" customHeight="1">
-      <c r="B115" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="C115" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D115" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E115" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F115" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G115" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="H115" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="I115" s="9" t="s">
+      <c r="B115" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J115" s="11" t="s">
@@ -4606,7 +4645,28 @@
       </c>
     </row>
     <row r="116" spans="2:10" ht="15" customHeight="1">
-      <c r="B116" s="12" t="s">
+      <c r="B116" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="C116" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D116" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E116" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F116" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G116" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="H116" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="I116" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J116" s="11" t="s">
@@ -4614,28 +4674,7 @@
       </c>
     </row>
     <row r="117" spans="2:10" ht="15" customHeight="1">
-      <c r="B117" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="C117" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D117" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E117" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F117" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G117" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="H117" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="I117" s="9" t="s">
+      <c r="B117" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J117" s="11" t="s">
@@ -4643,7 +4682,28 @@
       </c>
     </row>
     <row r="118" spans="2:10" ht="15" customHeight="1">
-      <c r="B118" s="12" t="s">
+      <c r="B118" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="C118" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D118" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E118" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F118" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G118" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="H118" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="I118" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J118" s="11" t="s">
@@ -4651,28 +4711,7 @@
       </c>
     </row>
     <row r="119" spans="2:10" ht="15" customHeight="1">
-      <c r="B119" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="C119" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D119" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E119" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F119" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G119" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="H119" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="I119" s="9" t="s">
+      <c r="B119" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J119" s="11" t="s">
@@ -4680,7 +4719,28 @@
       </c>
     </row>
     <row r="120" spans="2:10" ht="15" customHeight="1">
-      <c r="B120" s="12" t="s">
+      <c r="B120" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D120" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E120" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F120" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G120" s="9">
+        <v>494.90</v>
+      </c>
+      <c r="H120" s="10">
+        <v>0.0007707866354</v>
+      </c>
+      <c r="I120" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J120" s="11" t="s">
@@ -4688,29 +4748,29 @@
       </c>
     </row>
     <row r="121" spans="2:10" ht="15" customHeight="1">
-      <c r="B121" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="C121" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D121" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E121" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F121" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G121" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="H121" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="I121" s="9" t="s">
-        <v>13</v>
+      <c r="B121" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="C121" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="D121" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E121" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="F121" s="14">
+        <v>500000</v>
+      </c>
+      <c r="G121" s="15">
+        <v>494.90</v>
+      </c>
+      <c r="H121" s="16">
+        <v>0.0007707866354</v>
+      </c>
+      <c r="I121" s="15">
+        <v>5.61</v>
       </c>
       <c r="J121" s="11" t="s">
         <v>13</v>
@@ -4726,7 +4786,7 @@
     </row>
     <row r="123" spans="2:10" ht="15" customHeight="1">
       <c r="B123" s="7" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C123" s="8" t="s">
         <v>13</v>
@@ -4740,11 +4800,11 @@
       <c r="F123" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G123" s="9">
-        <v>4111.61</v>
-      </c>
-      <c r="H123" s="10">
-        <v>0.0068812000986</v>
+      <c r="G123" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="H123" s="10" t="s">
+        <v>230</v>
       </c>
       <c r="I123" s="9" t="s">
         <v>13</v>
@@ -4763,7 +4823,7 @@
     </row>
     <row r="125" spans="2:10" ht="15" customHeight="1">
       <c r="B125" s="7" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C125" s="8" t="s">
         <v>13</v>
@@ -4777,11 +4837,11 @@
       <c r="F125" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G125" s="9">
-        <v>699.9999965999999</v>
-      </c>
-      <c r="H125" s="10">
-        <v>0.0011715216291</v>
+      <c r="G125" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="H125" s="10" t="s">
+        <v>230</v>
       </c>
       <c r="I125" s="9" t="s">
         <v>13</v>
@@ -4792,20 +4852,6 @@
     </row>
     <row r="126" spans="2:10" ht="15" customHeight="1">
       <c r="B126" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="C126" s="13"/>
-      <c r="D126" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E126" s="13"/>
-      <c r="G126" s="15">
-        <v>699.9999965999999</v>
-      </c>
-      <c r="H126" s="16">
-        <v>0.0011715216291</v>
-      </c>
-      <c r="I126" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J126" s="11" t="s">
@@ -4813,7 +4859,28 @@
       </c>
     </row>
     <row r="127" spans="2:10" ht="15" customHeight="1">
-      <c r="B127" s="12" t="s">
+      <c r="B127" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="C127" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D127" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E127" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F127" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G127" s="9">
+        <v>6368.64</v>
+      </c>
+      <c r="H127" s="10">
+        <v>0.0099188979549</v>
+      </c>
+      <c r="I127" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J127" s="11" t="s">
@@ -4821,111 +4888,133 @@
       </c>
     </row>
     <row r="128" spans="2:10" ht="15" customHeight="1">
-      <c r="B128" s="17" t="s">
-        <v>241</v>
-      </c>
-      <c r="C128" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D128" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E128" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F128" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G128" s="18">
-        <v>-650.6834780595964</v>
-      </c>
-      <c r="H128" s="19">
-        <v>-0.0010889853885493828</v>
-      </c>
-      <c r="I128" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J128" s="20" t="s">
+      <c r="B128" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J128" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="129" spans="2:10" ht="15" customHeight="1">
-      <c r="B129" s="17" t="s">
-        <v>242</v>
-      </c>
-      <c r="C129" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D129" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E129" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F129" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G129" s="18">
-        <v>597513.50651854</v>
-      </c>
-      <c r="H129" s="19">
-        <v>0.9999999999957507</v>
-      </c>
-      <c r="I129" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J129" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="132" spans="2:9" ht="15" customHeight="1">
-      <c r="B132" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="C132" s="21"/>
-      <c r="D132" s="21"/>
-      <c r="E132" s="21"/>
-      <c r="F132" s="21"/>
-      <c r="G132" s="21"/>
-      <c r="H132" s="21"/>
-      <c r="I132" s="21"/>
-    </row>
-    <row r="133" spans="2:8" ht="15" customHeight="1">
-      <c r="B133" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="C133" s="21"/>
-      <c r="D133" s="21"/>
-      <c r="E133" s="21"/>
-      <c r="F133" s="21"/>
-      <c r="G133" s="21"/>
-      <c r="H133" s="21"/>
-    </row>
-    <row r="134" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B134" s="22" t="s">
-        <v>245</v>
-      </c>
-      <c r="C134" s="21"/>
-      <c r="D134" s="21"/>
-      <c r="E134" s="21"/>
-      <c r="F134" s="21"/>
-      <c r="G134" s="21"/>
-      <c r="H134" s="21"/>
-    </row>
-    <row r="135" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B135" s="22" t="s">
+      <c r="B129" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="C135" s="21"/>
-      <c r="D135" s="21"/>
-      <c r="E135" s="21"/>
-      <c r="F135" s="21"/>
-      <c r="G135" s="21"/>
-      <c r="H135" s="21"/>
-    </row>
-    <row r="136" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B136" s="22" t="s">
+      <c r="C129" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D129" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E129" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F129" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G129" s="9">
+        <v>399.9999966</v>
+      </c>
+      <c r="H129" s="10">
+        <v>0.0006229837372</v>
+      </c>
+      <c r="I129" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J129" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="130" spans="2:10" ht="15" customHeight="1">
+      <c r="B130" s="12" t="s">
         <v>247</v>
+      </c>
+      <c r="C130" s="13"/>
+      <c r="D130" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E130" s="13"/>
+      <c r="G130" s="15">
+        <v>399.9999966</v>
+      </c>
+      <c r="H130" s="16">
+        <v>0.0006229837372</v>
+      </c>
+      <c r="I130" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J130" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="131" spans="2:10" ht="15" customHeight="1">
+      <c r="B131" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J131" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="132" spans="2:10" ht="15" customHeight="1">
+      <c r="B132" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="C132" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D132" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E132" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F132" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G132" s="18">
+        <v>-472.8102077697404</v>
+      </c>
+      <c r="H132" s="19">
+        <v>-0.0007363826818513175</v>
+      </c>
+      <c r="I132" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J132" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="133" spans="2:10" ht="15" customHeight="1">
+      <c r="B133" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="C133" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D133" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E133" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F133" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G133" s="18">
+        <v>642071.32978883</v>
+      </c>
+      <c r="H133" s="19">
+        <v>0.9999999999953487</v>
+      </c>
+      <c r="I133" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J133" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="136" spans="2:9" ht="15" customHeight="1">
+      <c r="B136" s="13" t="s">
+        <v>250</v>
       </c>
       <c r="C136" s="21"/>
       <c r="D136" s="21"/>
@@ -4933,32 +5022,72 @@
       <c r="F136" s="21"/>
       <c r="G136" s="21"/>
       <c r="H136" s="21"/>
-    </row>
-    <row r="139" ht="15">
-      <c r="B139" s="21" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="154" ht="15">
-      <c r="B154" s="21" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="155" ht="15">
-      <c r="B155" s="21" t="s">
-        <v>250</v>
+      <c r="I136" s="21"/>
+    </row>
+    <row r="137" spans="2:8" ht="15" customHeight="1">
+      <c r="B137" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="C137" s="21"/>
+      <c r="D137" s="21"/>
+      <c r="E137" s="21"/>
+      <c r="F137" s="21"/>
+      <c r="G137" s="21"/>
+      <c r="H137" s="21"/>
+    </row>
+    <row r="138" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B138" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="C138" s="21"/>
+      <c r="D138" s="21"/>
+      <c r="E138" s="21"/>
+      <c r="F138" s="21"/>
+      <c r="G138" s="21"/>
+      <c r="H138" s="21"/>
+    </row>
+    <row r="139" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B139" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="C139" s="21"/>
+      <c r="D139" s="21"/>
+      <c r="E139" s="21"/>
+      <c r="F139" s="21"/>
+      <c r="G139" s="21"/>
+      <c r="H139" s="21"/>
+    </row>
+    <row r="140" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B140" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="C140" s="21"/>
+      <c r="D140" s="21"/>
+      <c r="E140" s="21"/>
+      <c r="F140" s="21"/>
+      <c r="G140" s="21"/>
+      <c r="H140" s="21"/>
+    </row>
+    <row r="143" ht="15">
+      <c r="B143" s="21" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="158" ht="15">
+      <c r="B158" s="21" t="s">
+        <v>256</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B134:H134"/>
-    <mergeCell ref="B135:H135"/>
-    <mergeCell ref="B136:H136"/>
+    <mergeCell ref="B138:H138"/>
+    <mergeCell ref="B139:H139"/>
+    <mergeCell ref="B140:H140"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B132:I132"/>
-    <mergeCell ref="B133:H133"/>
+    <mergeCell ref="B136:I136"/>
+    <mergeCell ref="B137:H137"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
